--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487883_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487883_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2853</v>
+        <v>5.8421</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6211</v>
+        <v>3.0311</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6642</v>
+        <v>2.811</v>
       </c>
       <c r="G2" t="n">
         <v>2.2928</v>
@@ -610,13 +610,13 @@
         <v>2.7055</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7437</v>
+        <v>1.3005</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7482</v>
+        <v>1.1583</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9295</v>
+        <v>2.8372</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1654</v>
+        <v>4.243</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7641</v>
+        <v>-1.4058</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7062</v>
+        <v>3.3057</v>
       </c>
       <c r="H3" t="n">
-        <v>0.209</v>
+        <v>1.917</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9152</v>
+        <v>1.3887</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2327</v>
+        <v>4.4733</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1151</v>
+        <v>1.3048</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>3.1685</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9389</v>
+        <v>-1.1676</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0939</v>
+        <v>0.6122</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0328</v>
+        <v>-1.7798</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R3" t="n">
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4921</v>
+        <v>0.4472</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3479</v>
+        <v>0.4315</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1442</v>
+        <v>0.0157</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9376</v>
+        <v>-0.7076</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.4152</v>
+        <v>1.6275</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4776</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8173</v>
+        <v>1.7573</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1313</v>
+        <v>0.052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.7054</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7335</v>
+        <v>-0.7062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0301</v>
+        <v>0.209</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7636</v>
+        <v>-0.9152</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9494</v>
+        <v>0.2327</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2834</v>
+        <v>0.1151</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2328</v>
+        <v>0.1176</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7841</v>
+        <v>-0.9389</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2533</v>
+        <v>0.0939</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5308</v>
+        <v>-1.0328</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>2.0812</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6965</v>
+        <v>1.3199</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8914</v>
+        <v>1.2345</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8051</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.23</v>
+        <v>-0.9376</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>-1.4152</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6482</v>
+        <v>1.1921</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1714</v>
+        <v>1.0114</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5232</v>
+        <v>0.1807</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3057</v>
+        <v>1.9746</v>
       </c>
       <c r="H5" t="n">
-        <v>1.917</v>
+        <v>1.0128</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3887</v>
+        <v>0.9617</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4733</v>
+        <v>2.3706</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3048</v>
+        <v>0.1639</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1685</v>
+        <v>2.2068</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1676</v>
+        <v>-0.3961</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6122</v>
+        <v>0.849</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7798</v>
+        <v>-1.245</v>
       </c>
       <c r="P5" t="n">
         <v>-0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2893</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7418</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.64</v>
+        <v>0.492</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1017</v>
+        <v>0.1012</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7076</v>
+        <v>-1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2616</v>
+        <v>0.2802</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1487</v>
+        <v>-0.024</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1129</v>
+        <v>0.3043</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9746</v>
+        <v>-2.7335</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0128</v>
+        <v>0.0301</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9617</v>
+        <v>-2.7636</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3706</v>
+        <v>-0.9494</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1639</v>
+        <v>0.2834</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2068</v>
+        <v>-1.2328</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3961</v>
+        <v>-1.7841</v>
       </c>
       <c r="N6" t="n">
-        <v>0.849</v>
+        <v>-0.2533</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.245</v>
+        <v>-1.5308</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8606</v>
+        <v>2.1594</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6681</v>
+        <v>1.736</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1924</v>
+        <v>0.4235</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7506</v>
+        <v>-1.3711</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1693</v>
+        <v>-2.0678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4187</v>
+        <v>0.6967</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3689</v>
+        <v>-4.7513</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7483</v>
+        <v>-1.7485</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6206</v>
+        <v>-3.0028</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1073</v>
+        <v>-3.2774</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5889</v>
+        <v>-1.1645</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5184</v>
+        <v>-2.1129</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2616</v>
+        <v>-1.4738</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1595</v>
+        <v>-0.5839</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1022</v>
+        <v>-0.8899</v>
       </c>
       <c r="P7" t="n">
+        <v>2.0812</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.2081</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.2893</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2416</v>
+        <v>1.0691</v>
       </c>
       <c r="T7" t="n">
-        <v>1.475</v>
+        <v>1.1878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7665999999999999</v>
+        <v>-0.1187</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4152</v>
+        <v>0.23</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2477</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9046</v>
+        <v>-2.2645</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4545</v>
+        <v>-2.3603</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.7513</v>
+        <v>-2.3689</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7485</v>
+        <v>-0.7483</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0028</v>
+        <v>-1.6206</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.2774</v>
+        <v>-1.1073</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1645</v>
+        <v>-0.5889</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1129</v>
+        <v>-0.5184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4738</v>
+        <v>-1.2616</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5839</v>
+        <v>-0.1595</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8899</v>
+        <v>-1.1022</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-2.2893</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.0812</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.2081</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.2893</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.5356</v>
+        <v>1.7277</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8011</v>
+        <v>1.284</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2655</v>
+        <v>0.4437</v>
       </c>
       <c r="V8" t="n">
-        <v>0.23</v>
+        <v>-1.4152</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>-0.2477</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0907</v>
+        <v>-2.5855</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7127</v>
+        <v>-1.6616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.622</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2266</v>
+        <v>-2.618</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7399</v>
+        <v>-1.6269</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4867</v>
+        <v>-0.9911</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9488</v>
+        <v>-1.9688</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.352</v>
+        <v>-1.3328</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5968</v>
+        <v>-0.636</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2778</v>
+        <v>-0.6492</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3879</v>
+        <v>-0.294</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8899</v>
+        <v>-0.3551</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0111</v>
+        <v>0.4945</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1924</v>
+        <v>0.3072</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1814</v>
+        <v>0.1873</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7076</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1509</v>
+        <v>-2.6033</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8126</v>
+        <v>-3.2841</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6617</v>
+        <v>0.6807</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4561</v>
+        <v>-3.2266</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5824</v>
+        <v>-1.7399</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8737</v>
+        <v>-1.4867</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9087</v>
+        <v>-1.9488</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.1372</v>
+        <v>-1.352</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7715</v>
+        <v>-0.5968</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5474</v>
+        <v>-1.2778</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4452</v>
+        <v>-0.3879</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1022</v>
+        <v>-0.8899</v>
       </c>
       <c r="P10" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.2487</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-3.3299</v>
       </c>
       <c r="R10" t="n">
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4478</v>
+        <v>0.4984</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3199</v>
+        <v>0.6211</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1279</v>
+        <v>-0.1226</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1061</v>
+        <v>-0.7076</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1061</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6613</v>
+        <v>-4.2453</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6493</v>
+        <v>-4.8189</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.012</v>
+        <v>0.5737</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.618</v>
+        <v>-4.4561</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6269</v>
+        <v>-2.5824</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9911</v>
+        <v>-1.8737</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9688</v>
+        <v>-2.9087</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3328</v>
+        <v>-2.1372</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.636</v>
+        <v>-0.7715</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6492</v>
+        <v>-1.5474</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.294</v>
+        <v>-0.4452</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3551</v>
+        <v>-1.1022</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8731</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5813</v>
+        <v>1.3534</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6805</v>
+        <v>1.3135</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0992</v>
+        <v>0.0398</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3351</v>
+        <v>0.1061</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1394</v>
+        <v>-1.160799999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.857899999999999</v>
+        <v>-5.879200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.718499999999999</v>
+        <v>4.7185</v>
       </c>
       <c r="G12" t="n">
         <v>-13.2875</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.102599999999999</v>
+        <v>-3.1026</v>
       </c>
       <c r="I12" t="n">
         <v>-10.1849</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.754200000000001</v>
+        <v>-2.7542</v>
       </c>
       <c r="K12" t="n">
         <v>-3.2439</v>
@@ -1375,13 +1375,13 @@
         <v>-10.5333</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1415000000000001</v>
+        <v>0.1414999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-10.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>7.284300000000001</v>
+        <v>7.2843</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5277</v>
@@ -1390,16 +1390,16 @@
         <v>20.8119</v>
       </c>
       <c r="S12" t="n">
-        <v>9.984699999999998</v>
+        <v>10.9633</v>
       </c>
       <c r="T12" t="n">
-        <v>8.7873</v>
+        <v>9.765899999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1975</v>
+        <v>1.1977</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.120699999999999</v>
+        <v>-6.120700000000001</v>
       </c>
       <c r="W12" t="n">
         <v>0.6368999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0752</v>
+        <v>4.118</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9469</v>
+        <v>2.5065</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1283</v>
+        <v>1.6114</v>
       </c>
       <c r="G13" t="n">
-        <v>2.693</v>
+        <v>5.7325</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5523</v>
+        <v>1.7957</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2453</v>
+        <v>3.9368</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4318</v>
+        <v>5.2387</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1645</v>
+        <v>1.0937</v>
       </c>
       <c r="L13" t="n">
-        <v>3.5963</v>
+        <v>4.145</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2612</v>
+        <v>0.4938</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6122</v>
+        <v>0.7019</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.351</v>
+        <v>-0.2082</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5731</v>
+        <v>-1.1546</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6524</v>
+        <v>-0.4429</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9206</v>
+        <v>-0.7117</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1228</v>
+        <v>-0.4599</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9553</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7465</v>
+        <v>4.0347</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9707</v>
+        <v>3.2684</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7663</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7325</v>
+        <v>2.693</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7957</v>
+        <v>-0.5523</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9368</v>
+        <v>3.2453</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2387</v>
+        <v>2.4318</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0937</v>
+        <v>-1.1645</v>
       </c>
       <c r="L14" t="n">
-        <v>4.145</v>
+        <v>3.5963</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4938</v>
+        <v>0.2612</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7019</v>
+        <v>0.6122</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2082</v>
+        <v>-0.351</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5261</v>
+        <v>-1.6135</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9786</v>
+        <v>-0.331</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5474</v>
+        <v>-1.2826</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4599</v>
+        <v>2.1228</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4599</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9963</v>
+        <v>1.3153</v>
       </c>
       <c r="E15" t="n">
         <v>0.4667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5295</v>
+        <v>0.8486</v>
       </c>
       <c r="G15" t="n">
         <v>1.3074</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7274</v>
+        <v>-0.4084</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5969</v>
+        <v>-0.2779</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.42</v>
+        <v>0.5335</v>
       </c>
       <c r="E16" t="n">
         <v>-0.4589</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8789</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3821</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1345</v>
+        <v>-1.021</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9388</v>
+        <v>-0.8252</v>
       </c>
       <c r="V16" t="n">
         <v>2.3528</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3049</v>
+        <v>0.324</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4612</v>
+        <v>-0.7827</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7661</v>
+        <v>1.1066</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4679</v>
@@ -1780,13 +1780,13 @@
         <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4593</v>
+        <v>-0.4402</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4501</v>
+        <v>0.1286</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9094</v>
+        <v>-0.5688</v>
       </c>
       <c r="V17" t="n">
         <v>3.2726</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3882</v>
+        <v>-0.233</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2203</v>
+        <v>-2.7592</v>
       </c>
       <c r="F18" t="n">
-        <v>0.832</v>
+        <v>2.5262</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3156</v>
+        <v>2.9914</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.648</v>
+        <v>1.9938</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9636</v>
+        <v>0.9977</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6096</v>
+        <v>1.6036</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3498</v>
+        <v>1.5734</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9594</v>
+        <v>0.0302</v>
       </c>
       <c r="M18" t="n">
-        <v>0.706</v>
+        <v>1.3878</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2982</v>
+        <v>0.4203</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0042</v>
+        <v>0.9675</v>
       </c>
       <c r="P18" t="n">
         <v>-2.4974</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>-4.1624</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4364</v>
+        <v>-0.8508</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0619</v>
+        <v>-0.2005</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4983</v>
+        <v>-0.6504</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>0.1238</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5181</v>
+        <v>-0.3833</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4545</v>
+        <v>-1.4346</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9365</v>
+        <v>1.0512</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2044</v>
+        <v>2.3156</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6844</v>
+        <v>-0.648</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.48</v>
+        <v>2.9636</v>
       </c>
       <c r="J19" t="n">
-        <v>3.376</v>
+        <v>1.6096</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2192</v>
+        <v>-0.3498</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1568</v>
+        <v>1.9594</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1716</v>
+        <v>0.706</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4652</v>
+        <v>-0.2982</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6368</v>
+        <v>1.0042</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.7461</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.4111</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3301</v>
+        <v>-0.4315</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5806</v>
+        <v>-0.1524</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9107</v>
+        <v>-0.2791</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3538</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Í. IBAÑEZ SERRANO</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.4046</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0392</v>
+        <v>-1.8831</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6919</v>
+        <v>1.4786</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8426</v>
+        <v>3.2044</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2409</v>
+        <v>3.6844</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6017</v>
+        <v>-0.48</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0392</v>
+        <v>3.376</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3.2192</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0392</v>
+        <v>0.1568</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8818</v>
+        <v>-0.1716</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2409</v>
+        <v>0.4652</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6409</v>
+        <v>-0.6368</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-3.7461</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.4111</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0183</v>
+        <v>-0.2166</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0183</v>
+        <v>-0.3685</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>Í. IBAÑEZ SERRANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8989</v>
+        <v>-0.7408</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0807</v>
+        <v>0.0392</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1817</v>
+        <v>-0.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9914</v>
+        <v>-0.8426</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9938</v>
+        <v>-0.2409</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9977</v>
+        <v>-0.6017</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6036</v>
+        <v>0.0392</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5734</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0302</v>
+        <v>0.0392</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3878</v>
+        <v>-0.8818</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4203</v>
+        <v>-0.2409</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9675</v>
+        <v>-0.6409</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4974</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5168</v>
+        <v>-0.1063</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5219</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9948</v>
+        <v>-0.1063</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0288</v>
+        <v>-0.8336</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7158</v>
+        <v>-1.6087</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7751</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2304</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4228</v>
+        <v>-0.2275</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.227</v>
+        <v>-0.139</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9167</v>
+        <v>-2.0189</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7506</v>
+        <v>-2.0721</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.166</v>
+        <v>0.0531</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0339</v>
@@ -2248,13 +2248,13 @@
         <v>2.0812</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1599</v>
+        <v>0.0576</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3849</v>
+        <v>0.0634</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.225</v>
+        <v>-0.0058</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8751</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.1395</v>
+        <v>5.711300000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-4.718500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>6.8578</v>
+        <v>10.4295</v>
       </c>
       <c r="G24" t="n">
         <v>13.2874</v>
@@ -2308,7 +2308,7 @@
         <v>10.6747</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7542</v>
+        <v>2.754199999999999</v>
       </c>
       <c r="N24" t="n">
         <v>3.2437</v>
@@ -2326,22 +2326,22 @@
         <v>13.5277</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.9849</v>
+        <v>-6.4128</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1973</v>
+        <v>-1.1976</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.7872</v>
+        <v>-5.2153</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1208</v>
+        <v>6.120800000000001</v>
       </c>
       <c r="W24" t="n">
         <v>6.7575</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6368</v>
+        <v>-0.6367999999999998</v>
       </c>
     </row>
   </sheetData>
